--- a/Rappi.xlsx
+++ b/Rappi.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2025_DigiLivo\Aliados\Rappi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Fabrica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66C27A9-B498-4C6C-AF98-57CAD39F43D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{90432604-9DEF-4D1B-BE9D-22FCCC081052}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Rappi" sheetId="1" r:id="rId1"/>
     <sheet name="Menú" sheetId="2" r:id="rId2"/>
-    <sheet name="materia_prima" sheetId="3" r:id="rId3"/>
+    <sheet name="lista_de_precios" sheetId="4" r:id="rId3"/>
+    <sheet name="materia_prima" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">lista_de_precios!$A$1:$E$22</definedName>
+  </definedNames>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
   <si>
     <t>23% comisiòn</t>
   </si>
@@ -98,19 +101,85 @@
   </si>
   <si>
     <t>%MC - Rappi</t>
+  </si>
+  <si>
+    <t>gaseosa</t>
+  </si>
+  <si>
+    <t>id_producto</t>
+  </si>
+  <si>
+    <t>nombre_producto</t>
+  </si>
+  <si>
+    <t>precio</t>
+  </si>
+  <si>
+    <t>CARNES - Churrasco Gaucho - 30</t>
+  </si>
+  <si>
+    <t>CARNES - Lomo de Cerdo -25</t>
+  </si>
+  <si>
+    <t>CARNES - Pechuga - 25</t>
+  </si>
+  <si>
+    <t>CARNES - Costillas BBQ - 25</t>
+  </si>
+  <si>
+    <t>CARNES - Sobrebarriga - 25</t>
+  </si>
+  <si>
+    <t>Bandeja Choriboni - 25</t>
+  </si>
+  <si>
+    <t>ChoriPan</t>
+  </si>
+  <si>
+    <t>Parrillada de 30</t>
+  </si>
+  <si>
+    <t>BEBIDA - Coca Cola ZERO</t>
+  </si>
+  <si>
+    <t>BEBIDA - Coca Cola 237ML</t>
+  </si>
+  <si>
+    <t>BEBIDA - Postobon 350ML</t>
+  </si>
+  <si>
+    <t>ChoriQueso</t>
+  </si>
+  <si>
+    <t>CARNES - Carne asada 30</t>
+  </si>
+  <si>
+    <t>BEBIDA - Jugo Hi 500mlt</t>
+  </si>
+  <si>
+    <t>BEBIDA - Botella de Agua - 600ml</t>
+  </si>
+  <si>
+    <t>HAMBURGUESA SENCILLLA</t>
+  </si>
+  <si>
+    <t>HAMBURGUESA EN COMBO</t>
+  </si>
+  <si>
+    <t>Chorizo con papa/arepa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,8 +210,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -179,6 +261,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -195,12 +289,12 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -213,8 +307,14 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="4" fillId="7" borderId="0" xfId="3" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
@@ -502,7 +602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537902D3-8418-4F4F-8834-154F042E7B0A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFFF9933"/>
   </sheetPr>
@@ -588,7 +688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57DC6F5-425B-41B0-9225-276621119978}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -675,6 +775,46 @@
         <v>0.22999999999999998</v>
       </c>
     </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2">
+        <f>+SUMIF(materia_prima!A:A,Menú!A3,materia_prima!C:C)</f>
+        <v>1200</v>
+      </c>
+      <c r="C3" s="2">
+        <v>3000</v>
+      </c>
+      <c r="D3" s="9">
+        <f>+C3-B3</f>
+        <v>1800</v>
+      </c>
+      <c r="E3" s="3">
+        <f>(C3-B3)/C3</f>
+        <v>0.6</v>
+      </c>
+      <c r="F3">
+        <f>+C3*23%</f>
+        <v>690</v>
+      </c>
+      <c r="G3" s="2">
+        <f>+C3-(B3+F3)</f>
+        <v>1110</v>
+      </c>
+      <c r="H3" s="3">
+        <f>(C3-(B3+F3))/C3</f>
+        <v>0.37</v>
+      </c>
+      <c r="I3" s="2">
+        <f>+D3-G3</f>
+        <v>690</v>
+      </c>
+      <c r="J3" s="3">
+        <f>+E3-H3</f>
+        <v>0.22999999999999998</v>
+      </c>
+    </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
@@ -721,11 +861,343 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B429684C-46F7-42EC-BBBD-6999BE565A1A}">
-  <dimension ref="A1:C2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="2" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="13">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="2">
+        <v>8000</v>
+      </c>
+      <c r="D2" s="2">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="2">
+        <v>10000</v>
+      </c>
+      <c r="D3" s="2">
+        <f>C3*(1+$D$1)</f>
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="2">
+        <f>C4*(1+$D$1)</f>
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3200</v>
+      </c>
+      <c r="D5" s="2">
+        <f>C5*(1+$D$1)</f>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3000</v>
+      </c>
+      <c r="D6" s="14">
+        <v>3500</v>
+      </c>
+      <c r="E6">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3000</v>
+      </c>
+      <c r="D7" s="14">
+        <v>3500</v>
+      </c>
+      <c r="H7">
+        <f>70000-8500</f>
+        <v>61500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2">
+        <v>4500</v>
+      </c>
+      <c r="D8" s="15">
+        <v>5500</v>
+      </c>
+      <c r="E8">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3500</v>
+      </c>
+      <c r="D9" s="16">
+        <v>4000</v>
+      </c>
+      <c r="E9">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2">
+        <v>25000</v>
+      </c>
+      <c r="D10" s="15">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2">
+        <v>30000</v>
+      </c>
+      <c r="D11" s="15">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2">
+        <v>30000</v>
+      </c>
+      <c r="D12" s="2">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="2">
+        <v>25000</v>
+      </c>
+      <c r="D13" s="2">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2">
+        <v>25000</v>
+      </c>
+      <c r="D14" s="2">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="2">
+        <v>25000</v>
+      </c>
+      <c r="D15" s="2">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="2">
+        <v>25000</v>
+      </c>
+      <c r="D16" s="2">
+        <v>29000</v>
+      </c>
+      <c r="H16">
+        <v>34500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>35</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="2">
+        <v>30000</v>
+      </c>
+      <c r="D17" s="2">
+        <f>C17*(1+$D$1)</f>
+        <v>37500</v>
+      </c>
+      <c r="H17">
+        <f>50000-H16</f>
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="2">
+        <v>22000</v>
+      </c>
+      <c r="D18" s="2">
+        <f>C18*(1+$D$1)</f>
+        <v>27500</v>
+      </c>
+      <c r="E18">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="2">
+        <v>17000</v>
+      </c>
+      <c r="D19" s="2">
+        <v>21500</v>
+      </c>
+      <c r="E19">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G21">
+        <f>6000*4</f>
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G22">
+        <v>32000</v>
+      </c>
+      <c r="H22">
+        <f>+G22-G21</f>
+        <v>8000</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E22">
+    <sortState ref="A2:E56">
+      <sortCondition ref="B1:B56"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -751,6 +1223,17 @@
         <v>700</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <v>1200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
